--- a/outputs/Chigwell Group - Gordon Court Pricing (CLEANED, external links stripped).xlsx
+++ b/outputs/Chigwell Group - Gordon Court Pricing (CLEANED, external links stripped).xlsx
@@ -15,6 +15,10 @@
   <sheets>
     <sheet name="Pricing Document " sheetId="84" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Pricing Document '!$B$1:$H$71</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Pricing Document '!$2:$7</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
